--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIII/LTAIPT_A63F33.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIII/LTAIPT_A63F33.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\SEGUNDO TRIMESTRE ABRIL-JUNIO 2024\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E721533-C437-4260-A75D-63BF8B6C7E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -12,14 +18,14 @@
     <sheet name="Tabla_436618" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="Hidden_14">Hidden_1!$A$1:$A$6</definedName>
+    <definedName name="Hidden_14">Hidden_1!$A$1:$A$4</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="96">
   <si>
     <t>48989</t>
   </si>
@@ -72,7 +78,7 @@
     <t>436623</t>
   </si>
   <si>
-    <t>436617</t>
+    <t>590338</t>
   </si>
   <si>
     <t>436626</t>
@@ -112,9 +118,6 @@
   </si>
   <si>
     <t>436624</t>
-  </si>
-  <si>
-    <t>436614</t>
   </si>
   <si>
     <t>436621</t>
@@ -178,97 +181,103 @@
     <t>Área(s) responsable(s) que genera(n), posee(n), publica(n) y actualizan la información</t>
   </si>
   <si>
-    <t>Fecha de validación</t>
-  </si>
-  <si>
     <t>Fecha de actualización</t>
   </si>
   <si>
     <t>Nota</t>
   </si>
   <si>
-    <t>2023</t>
+    <t>2024</t>
   </si>
   <si>
     <t>De concertación con el sector social</t>
   </si>
   <si>
+    <t>Condiciones Generales de Trabajo del Sindicato de Trabajadores Administrativos y de Intendencia del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>28/08/2023</t>
+  </si>
+  <si>
+    <t>Dirección General, Dirección Administrativa y Subdirección Jurídica</t>
+  </si>
+  <si>
+    <t>Regular las relaciones laborales entre el Colegio de Bachilleres del Estado de Tlaxcala  y los trabajadores administrativos y de intendencia.</t>
+  </si>
+  <si>
+    <t>Público- Estatal</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>31/12/2024</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202023/Sub%20Juridica/condiones24.pdf</t>
+  </si>
+  <si>
+    <t>Subdirección Jurídica</t>
+  </si>
+  <si>
+    <t>Contrato Colectivo de Trabajo del Sindicato de Trabajadores Académicos del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>02/09/2020</t>
+  </si>
+  <si>
+    <t>Regular las relaciones laborales entre el Colegio de Bachilleres del Estado de Tlaxcala y los trabajadores académicos.</t>
+  </si>
+  <si>
+    <t>01/02/2021</t>
+  </si>
+  <si>
+    <t>01/02/2023</t>
+  </si>
+  <si>
+    <t>01/02/2020</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202020/Subdireccion%20Juridica/3er_Trimestre/Contrato_Coletivo_de_Trabajo.pdf</t>
+  </si>
+  <si>
     <t>Condiciones Generales de Trabajo del Sindicato de Trabajdores Administrativos y de Intendencia del Colegio de Bachilleres del Estado de Tlaxcala</t>
   </si>
   <si>
-    <t>11/08/2021</t>
-  </si>
-  <si>
-    <t>Dirección General, Dirección Administrativa y Subdirección Jurídica</t>
-  </si>
-  <si>
-    <t>Regular las relaciones laborales entre el Colegio de Bachilleres del Estado de Tlaxcala  y los trabajadores administrativos y de intendencia.</t>
-  </si>
-  <si>
-    <t>Público- Estatal</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>01/01/2022</t>
-  </si>
-  <si>
-    <t>31/12/2023</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/Condiciones%20Generales%20de%20Trabajo%20STAICOBAT/CONDICIONES%20GRALES%20DE%20TRABAJO%20STAI%202021-2022.pdf</t>
-  </si>
-  <si>
-    <t>Subdirección Jurídica.</t>
-  </si>
-  <si>
-    <t>Contrato Colectivo de Trabajo del Sindicato de Trabajadores Académicos del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>02/09/2020</t>
-  </si>
-  <si>
-    <t>Regular las relaciones laborales entre el Colegio de Bachilleres del Estado de Tlaxcala y los trabajadores académicos.</t>
-  </si>
-  <si>
-    <t>01/02/2021</t>
-  </si>
-  <si>
-    <t>01/02/2023</t>
-  </si>
-  <si>
-    <t>01/02/2020</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202020/Subdireccion%20Juridica/3er_Trimestre/Contrato_Coletivo_de_Trabajo.pdf</t>
-  </si>
-  <si>
-    <t>436123BCE7FDF3ECD677BC33D599C84A</t>
-  </si>
-  <si>
-    <t>01/04/2023</t>
-  </si>
-  <si>
-    <t>30/06/2023</t>
-  </si>
-  <si>
-    <t>8101976</t>
-  </si>
-  <si>
-    <t>26/07/2023</t>
-  </si>
-  <si>
-    <t>2D08626EB6016289FE0ADEB8D8DD6642</t>
-  </si>
-  <si>
-    <t>8101975</t>
-  </si>
-  <si>
-    <t>De coordinación con el sector privado</t>
-  </si>
-  <si>
-    <t>De coordinación con el sector social</t>
+    <t>3C2250C15F606613F4FAD601E8D3B7AE</t>
+  </si>
+  <si>
+    <t>01/04/2024</t>
+  </si>
+  <si>
+    <t>30/06/2024</t>
+  </si>
+  <si>
+    <t>14422818</t>
+  </si>
+  <si>
+    <t>04/07/2024</t>
+  </si>
+  <si>
+    <t>69A33711ECDC002C857752E871EF0B56</t>
+  </si>
+  <si>
+    <t>14422817</t>
+  </si>
+  <si>
+    <t>175FAA8B1B0F0FDDE37CA131C62D9043</t>
+  </si>
+  <si>
+    <t>14422820</t>
+  </si>
+  <si>
+    <t>4F90974FB8F23A251D7235F4F676ACE8</t>
+  </si>
+  <si>
+    <t>14422819</t>
   </si>
   <si>
     <t>De concertación con el sector privado</t>
@@ -310,7 +319,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -409,6 +418,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -424,44 +436,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -489,14 +501,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -524,6 +553,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -535,180 +581,156 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:T11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="31" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="123.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="124.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="24.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="57" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="38.28515625" bestFit="1" customWidth="1"/>
@@ -718,19 +740,18 @@
     <col min="13" max="13" width="36.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="39" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="42" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="194.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="120.140625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="20" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -747,7 +768,7 @@
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -762,7 +783,7 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
     </row>
-    <row r="4" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -815,16 +836,13 @@
         <v>9</v>
       </c>
       <c r="S4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T4" t="s">
-        <v>12</v>
-      </c>
-      <c r="U4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>14</v>
       </c>
@@ -882,13 +900,10 @@
       <c r="T5" t="s">
         <v>32</v>
       </c>
-      <c r="U5" t="s">
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -909,203 +924,317 @@
       <c r="R6" s="5"/>
       <c r="S6" s="5"/>
       <c r="T6" s="5"/>
-      <c r="U6" s="5"/>
-    </row>
-    <row r="7" spans="1:21" ht="26.25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:20" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="I7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="N7" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="O7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="O7" s="2" t="s">
+      <c r="P7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="Q7" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="R7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="S7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="T7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="T7" s="2" t="s">
+    </row>
+    <row r="8" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="U7" s="2" t="s">
+      <c r="C8" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="F8" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="D9" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="G9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E8" s="3" t="s">
+      <c r="E10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="H8" s="3" t="s">
+      <c r="H11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="L11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S11" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="J9" s="3" t="s">
+      <c r="T11" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="T9" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:U6"/>
+    <mergeCell ref="A6:T6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -1114,7 +1243,7 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E199">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E193" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Hidden_14</formula1>
     </dataValidation>
   </dataValidations>
@@ -1123,38 +1252,28 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1163,7 +1282,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1189,34 +1308,34 @@
     </row>
     <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIII/LTAIPT_A63F33.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIII/LTAIPT_A63F33.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\SEGUNDO TRIMESTRE ABRIL-JUNIO 2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\TERCER TRIMESTRE JULIO-SEPTIEMBRE 2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E721533-C437-4260-A75D-63BF8B6C7E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C8E7260-03A3-4AE4-B260-4428F686F261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -187,9 +187,18 @@
     <t>Nota</t>
   </si>
   <si>
+    <t>319BF5AC42A9E679E03DC9D6A47E9936</t>
+  </si>
+  <si>
     <t>2024</t>
   </si>
   <si>
+    <t>01/07/2024</t>
+  </si>
+  <si>
+    <t>30/09/2024</t>
+  </si>
+  <si>
     <t>De concertación con el sector social</t>
   </si>
   <si>
@@ -202,6 +211,9 @@
     <t>Dirección General, Dirección Administrativa y Subdirección Jurídica</t>
   </si>
   <si>
+    <t>15970611</t>
+  </si>
+  <si>
     <t>Regular las relaciones laborales entre el Colegio de Bachilleres del Estado de Tlaxcala  y los trabajadores administrativos y de intendencia.</t>
   </si>
   <si>
@@ -223,12 +235,21 @@
     <t>Subdirección Jurídica</t>
   </si>
   <si>
+    <t>03/10/2024</t>
+  </si>
+  <si>
+    <t>812C356CD8CEC8F84A331C2F83D8121A</t>
+  </si>
+  <si>
     <t>Contrato Colectivo de Trabajo del Sindicato de Trabajadores Académicos del Colegio de Bachilleres del Estado de Tlaxcala</t>
   </si>
   <si>
     <t>02/09/2020</t>
   </si>
   <si>
+    <t>15970614</t>
+  </si>
+  <si>
     <t>Regular las relaciones laborales entre el Colegio de Bachilleres del Estado de Tlaxcala y los trabajadores académicos.</t>
   </si>
   <si>
@@ -244,40 +265,19 @@
     <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202020/Subdireccion%20Juridica/3er_Trimestre/Contrato_Coletivo_de_Trabajo.pdf</t>
   </si>
   <si>
+    <t>963FA78D41BE80A9D57658F5491FF39F</t>
+  </si>
+  <si>
+    <t>15970612</t>
+  </si>
+  <si>
+    <t>4FF86590DF9BBE01BAE3169417FF9816</t>
+  </si>
+  <si>
     <t>Condiciones Generales de Trabajo del Sindicato de Trabajdores Administrativos y de Intendencia del Colegio de Bachilleres del Estado de Tlaxcala</t>
   </si>
   <si>
-    <t>3C2250C15F606613F4FAD601E8D3B7AE</t>
-  </si>
-  <si>
-    <t>01/04/2024</t>
-  </si>
-  <si>
-    <t>30/06/2024</t>
-  </si>
-  <si>
-    <t>14422818</t>
-  </si>
-  <si>
-    <t>04/07/2024</t>
-  </si>
-  <si>
-    <t>69A33711ECDC002C857752E871EF0B56</t>
-  </si>
-  <si>
-    <t>14422817</t>
-  </si>
-  <si>
-    <t>175FAA8B1B0F0FDDE37CA131C62D9043</t>
-  </si>
-  <si>
-    <t>14422820</t>
-  </si>
-  <si>
-    <t>4F90974FB8F23A251D7235F4F676ACE8</t>
-  </si>
-  <si>
-    <t>14422819</t>
+    <t>15970613</t>
   </si>
   <si>
     <t>De concertación con el sector privado</t>
@@ -986,250 +986,250 @@
     </row>
     <row r="8" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="M8" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="N8" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="J8" s="3" t="s">
+      <c r="O8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="P8" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M8" s="3" t="s">
+      <c r="Q8" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="R8" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="N8" s="3" t="s">
+      <c r="S8" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="R8" s="3" t="s">
+      <c r="T8" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="P9" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="Q9" s="3" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="R9" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="T9" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="T9" s="3" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="K10" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="M10" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M10" s="3" t="s">
+      <c r="N10" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="R10" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="N10" s="3" t="s">
+      <c r="S10" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="R10" s="3" t="s">
+      <c r="T10" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="T10" s="3" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="G11" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>83</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K11" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="O11" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="P11" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="R11" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="S11" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="T11" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="S11" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="T11" s="3" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1243,7 +1243,7 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E193" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E192" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Hidden_14</formula1>
     </dataValidation>
   </dataValidations>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
